--- a/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_AnhTuanNB_010626.xlsx
+++ b/2. Báo cáo - giấy tờ/2. Bảo hành/Xuất nhập kho 2026/Xuất kho/Tháng 06/XKBH_AnhTuanNB_010626.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\2. Bảo hành\Xuất nhập kho 2026\Xuất kho\Tháng 06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF688B31-B711-488D-8C8C-7211179976FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F73FF96-2691-486F-BEA2-951498E5C6DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>STT</t>
   </si>
@@ -106,6 +106,15 @@
   </si>
   <si>
     <t>Tên Khách hàng: Đại lý anh Tuấn Ninh Bình</t>
+  </si>
+  <si>
+    <t>VT_Vỏ hộp_TG102LE</t>
+  </si>
+  <si>
+    <t>Chiếc</t>
+  </si>
+  <si>
+    <t>Làm mới nhập lại kho thiết bị đổi bảo hành cho đại lý Anh Tuấn Ninh Bình</t>
   </si>
 </sst>
 </file>
@@ -558,8 +567,8 @@
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>307038</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>164224</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -942,8 +951,8 @@
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" customWidth="1"/>
     <col min="2" max="6" width="15.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.42578125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.42578125" style="1" customWidth="1"/>
     <col min="9" max="14" width="9.140625" style="1" hidden="1" customWidth="1"/>
     <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
@@ -1074,14 +1083,24 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
+    <row r="10" spans="1:8" s="2" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="19">
+        <v>1</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="19">
+        <v>13</v>
+      </c>
       <c r="E10" s="19"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
+      <c r="G10" s="19" t="s">
+        <v>29</v>
+      </c>
       <c r="H10" s="19"/>
     </row>
     <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
